--- a/data_lake/freight/Baltic air freight index.xlsx
+++ b/data_lake/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADDD914-1C9B-154C-8C95-0C155ED02B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F4611A-9C34-C946-AC4F-A1449E6127EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17920" yWindow="780" windowWidth="18080" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="18">
   <si>
     <t>BAI80</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1684,6 +1684,9 @@
                 <c:pt idx="451">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="452">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3048,6 +3051,9 @@
                 </c:pt>
                 <c:pt idx="451">
                   <c:v>2423</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>2438</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4447,6 +4453,9 @@
                 <c:pt idx="451">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="452">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5811,6 +5820,9 @@
                 </c:pt>
                 <c:pt idx="451">
                   <c:v>1011</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>1104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7210,6 +7222,9 @@
                 <c:pt idx="451">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="452">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8574,6 +8589,9 @@
                 </c:pt>
                 <c:pt idx="451">
                   <c:v>4211</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>4186</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9973,6 +9991,9 @@
                 <c:pt idx="451">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="452">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11337,6 +11358,9 @@
                 </c:pt>
                 <c:pt idx="451">
                   <c:v>1179</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>1161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12736,6 +12760,9 @@
                 <c:pt idx="451">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="452">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14099,7 +14126,10 @@
                   <c:v>1398</c:v>
                 </c:pt>
                 <c:pt idx="451">
-                  <c:v>144</c:v>
+                  <c:v>1244</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>1162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15501,6 +15531,9 @@
                 <c:pt idx="451">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="452">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16865,6 +16898,9 @@
                 </c:pt>
                 <c:pt idx="451">
                   <c:v>5343</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>5415</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18280,6 +18316,9 @@
                 <c:pt idx="451">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="452">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19644,6 +19683,9 @@
                 </c:pt>
                 <c:pt idx="451">
                   <c:v>266</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>314</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20790,7 +20832,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K453"/>
+  <dimension ref="A1:K454"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
@@ -36648,13 +36690,48 @@
         <v>1179</v>
       </c>
       <c r="I453" s="13">
-        <v>144</v>
+        <v>1244</v>
       </c>
       <c r="J453" s="13">
         <v>266</v>
       </c>
       <c r="K453" s="13">
         <v>5343</v>
+      </c>
+    </row>
+    <row r="454" spans="1:11">
+      <c r="A454" s="10">
+        <v>46271</v>
+      </c>
+      <c r="B454" s="11">
+        <v>46272</v>
+      </c>
+      <c r="C454" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D454" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E454" s="13">
+        <v>2438</v>
+      </c>
+      <c r="F454" s="13">
+        <v>1104</v>
+      </c>
+      <c r="G454" s="13">
+        <v>4186</v>
+      </c>
+      <c r="H454" s="13">
+        <v>1161</v>
+      </c>
+      <c r="I454" s="13">
+        <v>1162</v>
+      </c>
+      <c r="J454" s="13">
+        <v>314</v>
+      </c>
+      <c r="K454" s="13">
+        <v>5415</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/Baltic air freight index.xlsx
+++ b/data_lake/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F4611A-9C34-C946-AC4F-A1449E6127EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C56CB4C-87F7-B249-9D55-C7B21382A8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17920" yWindow="780" windowWidth="18080" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="18">
   <si>
     <t>BAI80</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1687,6 +1687,9 @@
                 <c:pt idx="452">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="453">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3054,6 +3057,9 @@
                 </c:pt>
                 <c:pt idx="452">
                   <c:v>2438</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>2444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4456,6 +4462,9 @@
                 <c:pt idx="452">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="453">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5823,6 +5832,9 @@
                 </c:pt>
                 <c:pt idx="452">
                   <c:v>1104</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>1139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7225,6 +7237,9 @@
                 <c:pt idx="452">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="453">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8592,6 +8607,9 @@
                 </c:pt>
                 <c:pt idx="452">
                   <c:v>4186</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>4194</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9994,6 +10012,9 @@
                 <c:pt idx="452">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="453">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11361,6 +11382,9 @@
                 </c:pt>
                 <c:pt idx="452">
                   <c:v>1161</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>1055</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12763,6 +12787,9 @@
                 <c:pt idx="452">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="453">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14130,6 +14157,9 @@
                 </c:pt>
                 <c:pt idx="452">
                   <c:v>1162</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>1337</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15534,6 +15564,9 @@
                 <c:pt idx="452">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="453">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16901,6 +16934,9 @@
                 </c:pt>
                 <c:pt idx="452">
                   <c:v>5415</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>5376</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18319,6 +18355,9 @@
                 <c:pt idx="452">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="453">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19686,6 +19725,9 @@
                 </c:pt>
                 <c:pt idx="452">
                   <c:v>314</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>229</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20832,7 +20874,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K454"/>
+  <dimension ref="A1:K455"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
@@ -36732,6 +36774,41 @@
       </c>
       <c r="K454" s="13">
         <v>5415</v>
+      </c>
+    </row>
+    <row r="455" spans="1:11">
+      <c r="A455" s="10">
+        <v>46278</v>
+      </c>
+      <c r="B455" s="11">
+        <v>46279</v>
+      </c>
+      <c r="C455" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D455" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E455" s="13">
+        <v>2444</v>
+      </c>
+      <c r="F455" s="13">
+        <v>1139</v>
+      </c>
+      <c r="G455" s="13">
+        <v>4194</v>
+      </c>
+      <c r="H455" s="13">
+        <v>1055</v>
+      </c>
+      <c r="I455" s="13">
+        <v>1337</v>
+      </c>
+      <c r="J455" s="13">
+        <v>229</v>
+      </c>
+      <c r="K455" s="13">
+        <v>5376</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/Baltic air freight index.xlsx
+++ b/data_lake/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C56CB4C-87F7-B249-9D55-C7B21382A8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24666637-B6CB-C34F-B8C6-FF17FCF9F00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17920" yWindow="780" windowWidth="18080" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="18">
   <si>
     <t>BAI80</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1690,6 +1690,9 @@
                 <c:pt idx="453">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="454">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3060,6 +3063,9 @@
                 </c:pt>
                 <c:pt idx="453">
                   <c:v>2444</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>2466</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4465,6 +4471,9 @@
                 <c:pt idx="453">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="454">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5835,6 +5844,9 @@
                 </c:pt>
                 <c:pt idx="453">
                   <c:v>1139</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>1100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7240,6 +7252,9 @@
                 <c:pt idx="453">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="454">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8610,6 +8625,9 @@
                 </c:pt>
                 <c:pt idx="453">
                   <c:v>4194</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>4208</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10015,6 +10033,9 @@
                 <c:pt idx="453">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="454">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11385,6 +11406,9 @@
                 </c:pt>
                 <c:pt idx="453">
                   <c:v>1055</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>1160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12790,6 +12814,9 @@
                 <c:pt idx="453">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="454">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14160,6 +14187,9 @@
                 </c:pt>
                 <c:pt idx="453">
                   <c:v>1337</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>1351</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15567,6 +15597,9 @@
                 <c:pt idx="453">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="454">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16937,6 +16970,9 @@
                 </c:pt>
                 <c:pt idx="453">
                   <c:v>5376</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>5407</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18358,6 +18394,9 @@
                 <c:pt idx="453">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="454">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19728,6 +19767,9 @@
                 </c:pt>
                 <c:pt idx="453">
                   <c:v>229</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20874,7 +20916,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K455"/>
+  <dimension ref="A1:K456"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
@@ -36809,6 +36851,41 @@
       </c>
       <c r="K455" s="13">
         <v>5376</v>
+      </c>
+    </row>
+    <row r="456" spans="1:11">
+      <c r="A456" s="10">
+        <v>46285</v>
+      </c>
+      <c r="B456" s="11">
+        <v>46286</v>
+      </c>
+      <c r="C456" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D456" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E456" s="13">
+        <v>2466</v>
+      </c>
+      <c r="F456" s="13">
+        <v>1100</v>
+      </c>
+      <c r="G456" s="13">
+        <v>4208</v>
+      </c>
+      <c r="H456" s="13">
+        <v>1160</v>
+      </c>
+      <c r="I456" s="13">
+        <v>1351</v>
+      </c>
+      <c r="J456" s="13">
+        <v>238</v>
+      </c>
+      <c r="K456" s="13">
+        <v>5407</v>
       </c>
     </row>
   </sheetData>
